--- a/notas_estudiantes.xlsx
+++ b/notas_estudiantes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/322aa45d8efa2c13/PQ1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_26F8A11A51784A0E62355476585DCE3AA744D607" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68B19552-6D36-924F-B050-5C7EB6C67924}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_26F8A11A51784A0E62355476585DCE3AA744D607" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72971433-8438-BE41-A32A-891252D6680D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="281">
   <si>
     <t>LICENCIATURA</t>
   </si>
@@ -866,6 +866,15 @@
   </si>
   <si>
     <t>Parcial 4 (15%)</t>
+  </si>
+  <si>
+    <t>quiz 5</t>
+  </si>
+  <si>
+    <t>quiz 6</t>
+  </si>
+  <si>
+    <t>final</t>
   </si>
 </sst>
 </file>
@@ -956,10 +965,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -996,6 +1005,10 @@
 </file>
 
 <file path=xl/persons/person3.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person4.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -1284,12 +1297,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="24" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="11.5" customWidth="1"/>
     <col min="8" max="8" width="16.1640625" customWidth="1"/>
@@ -1298,7 +1313,7 @@
     <col min="15" max="15" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1341,12 +1356,20 @@
       <c r="N1" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="P1" s="3"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P1" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1366,14 +1389,14 @@
         <v>15</v>
       </c>
       <c r="G2">
-        <f>F2*0.15+I2*0.025+J2*0.025+K2*0.025+L2*0.025+M2*0.15+N2*0.15+O2*0.2</f>
-        <v>10.887499999999999</v>
+        <f>F2*0.15+I2*0.025+J2*0.025+K2*0.025+L2*0.025+M2*0.15+N2*0.15+O2*0.2+P2*0.025+Q2*0.025+R2*0.2</f>
+        <v>15.4125</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J2">
         <v>18</v>
@@ -1393,8 +1416,14 @@
       <c r="O2">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q2">
+        <v>19</v>
+      </c>
+      <c r="R2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1414,14 +1443,14 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G66" si="0">F3*0.15+I3*0.025+J3*0.025+K3*0.025+L3*0.025+M3*0.15+N3*0.15+O3*0.2</f>
-        <v>12.649999999999999</v>
+        <f t="shared" ref="G3:G66" si="0">F3*0.15+I3*0.025+J3*0.025+K3*0.025+L3*0.025+M3*0.15+N3*0.15+O3*0.2+P3*0.025+Q3*0.025+R3*0.2</f>
+        <v>19.125</v>
       </c>
       <c r="H3">
         <v>100</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <v>15</v>
@@ -1433,16 +1462,25 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N3">
         <v>20</v>
       </c>
       <c r="O3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+      <c r="P3">
+        <v>19</v>
+      </c>
+      <c r="Q3">
+        <v>20</v>
+      </c>
+      <c r="R3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1460,7 +1498,7 @@
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>3.5249999999999999</v>
+        <v>5.375</v>
       </c>
       <c r="H4">
         <v>62.5</v>
@@ -1483,8 +1521,14 @@
       <c r="N4">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P4">
+        <v>18</v>
+      </c>
+      <c r="R4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1523,7 +1567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1568,7 +1612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1589,7 +1633,7 @@
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>13.162500000000001</v>
+        <v>18.137500000000003</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -1615,8 +1659,17 @@
       <c r="O7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7">
+        <v>19</v>
+      </c>
+      <c r="Q7">
+        <v>20</v>
+      </c>
+      <c r="R7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1637,7 +1690,7 @@
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>1.8499999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -1663,8 +1716,17 @@
       <c r="O8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8">
+        <v>6</v>
+      </c>
+      <c r="Q8">
+        <v>4</v>
+      </c>
+      <c r="R8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1685,7 +1747,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>4.8125</v>
+        <v>6.6375000000000002</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -1711,8 +1773,17 @@
       <c r="O9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9">
+        <v>10</v>
+      </c>
+      <c r="Q9">
+        <v>7</v>
+      </c>
+      <c r="R9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1733,7 +1804,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>11.625</v>
+        <v>16.05</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -1757,10 +1828,19 @@
         <v>20</v>
       </c>
       <c r="O10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="P10">
+        <v>13</v>
+      </c>
+      <c r="Q10">
+        <v>20</v>
+      </c>
+      <c r="R10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1781,7 +1861,7 @@
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>11.6625</v>
+        <v>16.5625</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -1805,10 +1885,19 @@
         <v>18</v>
       </c>
       <c r="O11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>16.5</v>
+      </c>
+      <c r="P11">
+        <v>16</v>
+      </c>
+      <c r="Q11">
+        <v>16</v>
+      </c>
+      <c r="R11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1829,7 +1918,7 @@
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
-        <v>7.9249999999999989</v>
+        <v>12.299999999999999</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -1853,10 +1942,19 @@
         <v>20</v>
       </c>
       <c r="O12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="P12">
+        <v>19</v>
+      </c>
+      <c r="Q12">
+        <v>20</v>
+      </c>
+      <c r="R12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1895,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1940,7 +2038,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1961,7 +2059,7 @@
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>3.7625000000000002</v>
+        <v>7.3625000000000007</v>
       </c>
       <c r="H15">
         <v>100</v>
@@ -1985,10 +2083,19 @@
         <v>3</v>
       </c>
       <c r="O15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>18</v>
+      </c>
+      <c r="Q15">
+        <v>6</v>
+      </c>
+      <c r="R15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2009,7 +2116,7 @@
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
-        <v>8.4875000000000007</v>
+        <v>12.0375</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -2035,8 +2142,17 @@
       <c r="O16">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P16">
+        <v>18</v>
+      </c>
+      <c r="Q16">
+        <v>20</v>
+      </c>
+      <c r="R16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -2081,7 +2197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2102,7 +2218,7 @@
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>0.96249999999999991</v>
+        <v>1.2874999999999999</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -2122,8 +2238,11 @@
       <c r="M18">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -2141,7 +2260,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>6.3624999999999998</v>
+        <v>11.437499999999998</v>
       </c>
       <c r="H19">
         <v>62.5</v>
@@ -2162,13 +2281,22 @@
         <v>12</v>
       </c>
       <c r="N19">
+        <v>16</v>
+      </c>
+      <c r="O19">
+        <v>16</v>
+      </c>
+      <c r="P19">
+        <v>19</v>
+      </c>
+      <c r="Q19">
+        <v>20</v>
+      </c>
+      <c r="R19">
         <v>10</v>
       </c>
-      <c r="O19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2189,7 +2317,7 @@
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>7.0749999999999993</v>
+        <v>8.875</v>
       </c>
       <c r="H20">
         <v>100</v>
@@ -2215,8 +2343,17 @@
       <c r="O20">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P20">
+        <v>16</v>
+      </c>
+      <c r="Q20">
+        <v>8</v>
+      </c>
+      <c r="R20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -2234,7 +2371,7 @@
       </c>
       <c r="G21">
         <f t="shared" si="0"/>
-        <v>3.4499999999999997</v>
+        <v>3.9249999999999998</v>
       </c>
       <c r="H21">
         <v>62.5</v>
@@ -2257,8 +2394,11 @@
       <c r="N21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -2279,7 +2419,7 @@
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
-        <v>3.75</v>
+        <v>4.1749999999999998</v>
       </c>
       <c r="H22">
         <v>100</v>
@@ -2302,8 +2442,11 @@
       <c r="N22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2324,7 +2467,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="0"/>
-        <v>6.6875</v>
+        <v>10.5375</v>
       </c>
       <c r="H23">
         <v>100</v>
@@ -2348,10 +2491,19 @@
         <v>11</v>
       </c>
       <c r="O23">
+        <v>18</v>
+      </c>
+      <c r="P23">
+        <v>12</v>
+      </c>
+      <c r="Q23">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="R23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -2393,7 +2545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -2414,7 +2566,7 @@
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>3.7624999999999997</v>
+        <v>4.2374999999999998</v>
       </c>
       <c r="H25">
         <v>100</v>
@@ -2440,8 +2592,14 @@
       <c r="O25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P25">
+        <v>14</v>
+      </c>
+      <c r="Q25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -2462,7 +2620,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="0"/>
-        <v>3.7625000000000002</v>
+        <v>4.2374999999999998</v>
       </c>
       <c r="H26">
         <v>100</v>
@@ -2488,8 +2646,11 @@
       <c r="O26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P26">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -2528,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -2549,7 +2710,7 @@
       </c>
       <c r="G28">
         <f t="shared" si="0"/>
-        <v>3.5250000000000004</v>
+        <v>6.2750000000000004</v>
       </c>
       <c r="H28">
         <v>100</v>
@@ -2575,8 +2736,17 @@
       <c r="O28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P28">
+        <v>8</v>
+      </c>
+      <c r="Q28">
+        <v>14</v>
+      </c>
+      <c r="R28">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -2597,7 +2767,7 @@
       </c>
       <c r="G29">
         <f t="shared" si="0"/>
-        <v>3.2375000000000003</v>
+        <v>3.6375000000000002</v>
       </c>
       <c r="H29">
         <v>100</v>
@@ -2620,8 +2790,11 @@
       <c r="N29">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P29">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -2642,7 +2815,7 @@
       </c>
       <c r="G30">
         <f t="shared" si="0"/>
-        <v>5.8875000000000002</v>
+        <v>6.0875000000000004</v>
       </c>
       <c r="H30">
         <v>100</v>
@@ -2668,8 +2841,11 @@
       <c r="O30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -2690,7 +2866,7 @@
       </c>
       <c r="G31">
         <f t="shared" si="0"/>
-        <v>2.7</v>
+        <v>3.0250000000000004</v>
       </c>
       <c r="H31">
         <v>100</v>
@@ -2705,7 +2881,7 @@
         <v>8</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M31">
         <v>1</v>
@@ -2716,8 +2892,11 @@
       <c r="O31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2738,7 +2917,7 @@
       </c>
       <c r="G32">
         <f t="shared" si="0"/>
-        <v>7.2250000000000005</v>
+        <v>11.775</v>
       </c>
       <c r="H32">
         <v>100</v>
@@ -2764,8 +2943,17 @@
       <c r="O32">
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P32">
+        <v>19</v>
+      </c>
+      <c r="Q32">
+        <v>19</v>
+      </c>
+      <c r="R32">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -2786,7 +2974,7 @@
       </c>
       <c r="G33">
         <f t="shared" si="0"/>
-        <v>2.1125000000000003</v>
+        <v>2.8375000000000004</v>
       </c>
       <c r="H33">
         <v>100</v>
@@ -2804,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="M33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -2812,8 +3000,11 @@
       <c r="O33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P33">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -2834,7 +3025,7 @@
       </c>
       <c r="G34">
         <f t="shared" si="0"/>
-        <v>6.4</v>
+        <v>10.725</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -2858,10 +3049,19 @@
         <v>3</v>
       </c>
       <c r="O34">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="P34">
+        <v>17</v>
+      </c>
+      <c r="Q34">
+        <v>12</v>
+      </c>
+      <c r="R34">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -2882,7 +3082,7 @@
       </c>
       <c r="G35">
         <f t="shared" si="0"/>
-        <v>11.1875</v>
+        <v>16.9375</v>
       </c>
       <c r="H35">
         <v>100</v>
@@ -2906,10 +3106,19 @@
         <v>20</v>
       </c>
       <c r="O35">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="P35">
+        <v>18</v>
+      </c>
+      <c r="Q35">
+        <v>20</v>
+      </c>
+      <c r="R35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -2951,7 +3160,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -2972,7 +3181,7 @@
       </c>
       <c r="G37">
         <f t="shared" si="0"/>
-        <v>4.2625000000000002</v>
+        <v>4.3875000000000002</v>
       </c>
       <c r="H37">
         <v>100</v>
@@ -2998,8 +3207,11 @@
       <c r="O37">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -3020,7 +3232,7 @@
       </c>
       <c r="G38">
         <f t="shared" si="0"/>
-        <v>3.1749999999999998</v>
+        <v>4.125</v>
       </c>
       <c r="H38">
         <v>100</v>
@@ -3043,8 +3255,14 @@
       <c r="O38">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P38">
+        <v>14</v>
+      </c>
+      <c r="R38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -3065,7 +3283,7 @@
       </c>
       <c r="G39">
         <f t="shared" si="0"/>
-        <v>1.5374999999999999</v>
+        <v>1.6875</v>
       </c>
       <c r="H39">
         <v>100</v>
@@ -3091,8 +3309,11 @@
       <c r="O39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>31</v>
       </c>
@@ -3131,7 +3352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>31</v>
       </c>
@@ -3152,7 +3373,7 @@
       </c>
       <c r="G41">
         <f t="shared" si="0"/>
-        <v>7.4625000000000004</v>
+        <v>10.3375</v>
       </c>
       <c r="H41">
         <v>100</v>
@@ -3176,10 +3397,19 @@
         <v>1.5</v>
       </c>
       <c r="O41">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+      <c r="P41">
+        <v>7</v>
+      </c>
+      <c r="Q41">
+        <v>16</v>
+      </c>
+      <c r="R41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -3200,7 +3430,7 @@
       </c>
       <c r="G42">
         <f t="shared" si="0"/>
-        <v>3.8875000000000002</v>
+        <v>5.2374999999999998</v>
       </c>
       <c r="H42">
         <v>100</v>
@@ -3226,8 +3456,17 @@
       <c r="O42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P42">
+        <v>7</v>
+      </c>
+      <c r="Q42">
+        <v>7</v>
+      </c>
+      <c r="R42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>31</v>
       </c>
@@ -3272,7 +3511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -3293,7 +3532,7 @@
       </c>
       <c r="G44">
         <f t="shared" si="0"/>
-        <v>2.3250000000000002</v>
+        <v>3</v>
       </c>
       <c r="H44">
         <v>100</v>
@@ -3319,8 +3558,14 @@
       <c r="O44">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P44">
+        <v>11</v>
+      </c>
+      <c r="R44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>31</v>
       </c>
@@ -3341,7 +3586,7 @@
       </c>
       <c r="G45">
         <f t="shared" si="0"/>
-        <v>2.5124999999999997</v>
+        <v>2.6624999999999996</v>
       </c>
       <c r="H45">
         <v>100</v>
@@ -3364,8 +3609,11 @@
       <c r="N45">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -3386,7 +3634,7 @@
       </c>
       <c r="G46">
         <f t="shared" si="0"/>
-        <v>9.2875000000000014</v>
+        <v>11.887500000000003</v>
       </c>
       <c r="H46">
         <v>100</v>
@@ -3412,8 +3660,17 @@
       <c r="O46">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P46">
+        <v>16</v>
+      </c>
+      <c r="Q46">
+        <v>16</v>
+      </c>
+      <c r="R46">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -3434,7 +3691,7 @@
       </c>
       <c r="G47">
         <f t="shared" si="0"/>
-        <v>4.2874999999999996</v>
+        <v>4.7624999999999993</v>
       </c>
       <c r="H47">
         <v>100</v>
@@ -3460,8 +3717,11 @@
       <c r="O47">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P47">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -3482,7 +3742,7 @@
       </c>
       <c r="G48">
         <f t="shared" si="0"/>
-        <v>1.2625</v>
+        <v>1.5375000000000001</v>
       </c>
       <c r="H48">
         <v>100</v>
@@ -3508,8 +3768,11 @@
       <c r="O48">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P48">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>31</v>
       </c>
@@ -3530,7 +3793,7 @@
       </c>
       <c r="G49">
         <f t="shared" si="0"/>
-        <v>3.0625</v>
+        <v>3.2374999999999998</v>
       </c>
       <c r="H49">
         <v>100</v>
@@ -3556,8 +3819,11 @@
       <c r="O49">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>31</v>
       </c>
@@ -3578,7 +3844,7 @@
       </c>
       <c r="G50">
         <f t="shared" si="0"/>
-        <v>7.5874999999999995</v>
+        <v>10.737499999999999</v>
       </c>
       <c r="H50">
         <v>100</v>
@@ -3604,8 +3870,17 @@
       <c r="O50">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P50">
+        <v>6</v>
+      </c>
+      <c r="Q50">
+        <v>16</v>
+      </c>
+      <c r="R50">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -3626,7 +3901,7 @@
       </c>
       <c r="G51">
         <f t="shared" si="0"/>
-        <v>10.0625</v>
+        <v>16.137499999999999</v>
       </c>
       <c r="H51">
         <v>100</v>
@@ -3641,19 +3916,28 @@
         <v>16.5</v>
       </c>
       <c r="L51">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N51">
         <v>12</v>
       </c>
       <c r="O51">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="P51">
+        <v>19</v>
+      </c>
+      <c r="Q51">
+        <v>20</v>
+      </c>
+      <c r="R51">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -3674,7 +3958,7 @@
       </c>
       <c r="G52">
         <f t="shared" si="0"/>
-        <v>3.7124999999999999</v>
+        <v>4.1124999999999998</v>
       </c>
       <c r="H52">
         <v>100</v>
@@ -3697,8 +3981,11 @@
       <c r="N52">
         <v>6</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P52">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -3719,7 +4006,7 @@
       </c>
       <c r="G53">
         <f t="shared" si="0"/>
-        <v>7.4</v>
+        <v>11.399999999999999</v>
       </c>
       <c r="H53">
         <v>100</v>
@@ -3745,8 +4032,17 @@
       <c r="O53">
         <v>12</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P53">
+        <v>19</v>
+      </c>
+      <c r="Q53">
+        <v>13</v>
+      </c>
+      <c r="R53">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -3791,7 +4087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>31</v>
       </c>
@@ -3812,7 +4108,7 @@
       </c>
       <c r="G55">
         <f t="shared" si="0"/>
-        <v>5.9124999999999996</v>
+        <v>9.5374999999999996</v>
       </c>
       <c r="H55">
         <v>100</v>
@@ -3833,13 +4129,22 @@
         <v>9</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O55">
         <v>10</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P55">
+        <v>10</v>
+      </c>
+      <c r="Q55">
+        <v>15</v>
+      </c>
+      <c r="R55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -3857,7 +4162,7 @@
       </c>
       <c r="G56">
         <f t="shared" si="0"/>
-        <v>1.8</v>
+        <v>6.4249999999999998</v>
       </c>
       <c r="H56">
         <v>62.5</v>
@@ -3881,10 +4186,19 @@
         <v>8</v>
       </c>
       <c r="O56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="P56">
+        <v>17</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -3902,7 +4216,7 @@
       </c>
       <c r="G57">
         <f t="shared" si="0"/>
-        <v>0.97500000000000009</v>
+        <v>1.0750000000000002</v>
       </c>
       <c r="H57">
         <v>62.5</v>
@@ -3925,8 +4239,11 @@
       <c r="N57">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -3971,7 +4288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -4016,7 +4333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>31</v>
       </c>
@@ -4037,7 +4354,7 @@
       </c>
       <c r="G60">
         <f t="shared" si="0"/>
-        <v>2.7375000000000003</v>
+        <v>4.0875000000000004</v>
       </c>
       <c r="H60">
         <v>100</v>
@@ -4063,8 +4380,17 @@
       <c r="O60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P60">
+        <v>5</v>
+      </c>
+      <c r="Q60">
+        <v>1</v>
+      </c>
+      <c r="R60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -4085,7 +4411,7 @@
       </c>
       <c r="G61">
         <f t="shared" si="0"/>
-        <v>2.125</v>
+        <v>2.6</v>
       </c>
       <c r="H61">
         <v>100</v>
@@ -4108,8 +4434,11 @@
       <c r="N61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P61">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -4154,7 +4483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>31</v>
       </c>
@@ -4175,7 +4504,7 @@
       </c>
       <c r="G63">
         <f t="shared" si="0"/>
-        <v>5.15</v>
+        <v>5.4750000000000005</v>
       </c>
       <c r="H63">
         <v>100</v>
@@ -4201,8 +4530,11 @@
       <c r="O63">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P63">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -4244,7 +4576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -4265,7 +4597,7 @@
       </c>
       <c r="G65">
         <f t="shared" si="0"/>
-        <v>4.3624999999999998</v>
+        <v>4.9375</v>
       </c>
       <c r="H65">
         <v>100</v>
@@ -4291,8 +4623,14 @@
       <c r="O65">
         <v>4</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P65">
+        <v>8</v>
+      </c>
+      <c r="Q65">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>31</v>
       </c>
@@ -4313,7 +4651,7 @@
       </c>
       <c r="G66">
         <f t="shared" si="0"/>
-        <v>4.7875000000000005</v>
+        <v>7.3625000000000007</v>
       </c>
       <c r="H66">
         <v>100</v>
@@ -4339,8 +4677,17 @@
       <c r="O66">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P66">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>7</v>
+      </c>
+      <c r="R66">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -4360,8 +4707,8 @@
         <v>3</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67" si="1">F67*0.15+I67*0.025+J67*0.025+K67*0.025+L67*0.025+M67*0.15+N67*0.15+O67*0.2</f>
-        <v>3.55</v>
+        <f t="shared" ref="G67" si="1">F67*0.15+I67*0.025+J67*0.025+K67*0.025+L67*0.025+M67*0.15+N67*0.15+O67*0.2+P67*0.025+Q67*0.025+R67*0.2</f>
+        <v>3.7</v>
       </c>
       <c r="H67">
         <v>100</v>
@@ -4379,7 +4726,7 @@
         <v>12</v>
       </c>
       <c r="M67">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="N67">
         <v>2</v>

--- a/notas_estudiantes.xlsx
+++ b/notas_estudiantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/322aa45d8efa2c13/PQ1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_26F8A11A51784A0E62355476585DCE3AA744D607" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72971433-8438-BE41-A32A-891252D6680D}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="11_26F8A11A51784A0E62355476585DCE3AA744D607" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B715A8D4-AB84-7240-A9F6-03BE5AA47AB4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas" sheetId="1" r:id="rId1"/>
@@ -1009,6 +1009,10 @@
 </file>
 
 <file path=xl/persons/person4.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person5.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -2258,9 +2262,12 @@
       <c r="E19" t="s">
         <v>86</v>
       </c>
+      <c r="F19">
+        <v>9</v>
+      </c>
       <c r="G19">
         <f t="shared" si="0"/>
-        <v>11.437499999999998</v>
+        <v>12.7875</v>
       </c>
       <c r="H19">
         <v>62.5</v>

--- a/notas_estudiantes.xlsx
+++ b/notas_estudiantes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/322aa45d8efa2c13/PQ1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="11_26F8A11A51784A0E62355476585DCE3AA744D607" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B715A8D4-AB84-7240-A9F6-03BE5AA47AB4}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_26F8A11A51784A0E62355476585DCE3AA744D607" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A45280D0-FAE3-FF45-98DF-1456D6772B70}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35600" yWindow="-80" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notas" sheetId="1" r:id="rId1"/>
@@ -1013,6 +1013,14 @@
 </file>
 
 <file path=xl/persons/person5.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person6.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person7.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -1308,7 +1316,7 @@
     <col min="2" max="2" width="9.1640625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" customWidth="1"/>
-    <col min="5" max="5" width="24" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="11.5" customWidth="1"/>
     <col min="8" max="8" width="16.1640625" customWidth="1"/>
@@ -3380,7 +3388,7 @@
       </c>
       <c r="G41">
         <f t="shared" si="0"/>
-        <v>10.3375</v>
+        <v>11.987500000000001</v>
       </c>
       <c r="H41">
         <v>100</v>
@@ -3401,7 +3409,7 @@
         <v>19.5</v>
       </c>
       <c r="N41">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="O41">
         <v>13</v>
